--- a/survey_templates/036_volleyball_team_snack_preferences_survey--survey_templates.xlsx
+++ b/survey_templates/036_volleyball_team_snack_preferences_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'none',_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'None', 'value': 'none'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'vegetarian',_'value':_'vegetarian'}</t>
+          <t>vegetarian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Vegetarian', 'value': 'vegetarian'}</t>
+          <t>Vegetarian</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegan',_'value':_'vegan'}</t>
+          <t>vegan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegan', 'value': 'vegan'}</t>
+          <t>Vegan</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'gluten-free',_'value':_'gluten-free'}</t>
+          <t>gluten-free</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Gluten-free', 'value': 'gluten-free'}</t>
+          <t>Gluten-free</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'water',_'value':_'water'}</t>
+          <t>water</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Water', 'value': 'water'}</t>
+          <t>Water</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'fruits',_'value':_'fruits'}</t>
+          <t>fruits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Fruits', 'value': 'fruits'}</t>
+          <t>Fruits</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'vegetables',_'value':_'vegetables'}</t>
+          <t>vegetables</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Vegetables', 'value': 'vegetables'}</t>
+          <t>Vegetables</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'cheese',_'value':_'cheese'}</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Cheese', 'value': 'cheese'}</t>
+          <t>Cheese</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'granola',_'value':_'granola'}</t>
+          <t>granola</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Granola', 'value': 'granola'}</t>
+          <t>Granola</t>
         </is>
       </c>
     </row>
